--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-12/2026-09-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-13/2026-09-13</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,61 +37,55 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,004.77</t>
-  </si>
-  <si>
-    <t>3,001.55</t>
+    <t>2,912.65</t>
+  </si>
+  <si>
+    <t>2,911.15</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,277.34</t>
+  </si>
+  <si>
+    <t>3,273.60</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,873.41</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,842.49</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,173.76</t>
+  </si>
+  <si>
+    <t>2,171.00</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,627.38</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,783.26</t>
-  </si>
-  <si>
-    <t>3,777.10</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,249.28</t>
-  </si>
-  <si>
-    <t>3,234.30</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,738.50</t>
-  </si>
-  <si>
-    <t>3,735.90</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,632.67</t>
+    <t>1,098.50</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>17,035.86</t>
-  </si>
-  <si>
-    <t>17,008.90</t>
-  </si>
-  <si>
-    <t>1,063</t>
+    <t>16,178.15</t>
+  </si>
+  <si>
+    <t>16,170.15</t>
   </si>
 </sst>
 </file>
@@ -507,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.22</v>
+        <v>1.5</v>
       </c>
       <c r="E3">
-        <v>67.32</v>
+        <v>41.95</v>
       </c>
       <c r="F3">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,36 +518,36 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="E4">
-        <v>26.97</v>
+        <v>18.18</v>
       </c>
       <c r="F4">
-        <v>121</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35.36</v>
+        <v>36.1</v>
       </c>
       <c r="F5">
-        <v>254</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -564,76 +558,76 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>14.98</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21.3</v>
+        <v>40.95</v>
       </c>
       <c r="F6">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
       <c r="D7">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="E7">
-        <v>13.48</v>
+        <v>19.38</v>
       </c>
       <c r="F7">
-        <v>253</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>21.37</v>
+        <v>7.99</v>
       </c>
       <c r="F8">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
       <c r="D9">
-        <v>26.96</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>185.8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
+        <v>164.55</v>
+      </c>
+      <c r="F9">
+        <v>929</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-13/2026-09-13</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-14/2026-09-14</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,439.80</t>
+  </si>
+  <si>
+    <t>1,427.54</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,380.38</t>
+  </si>
+  <si>
+    <t>1,379.20</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,912.65</t>
-  </si>
-  <si>
-    <t>2,911.15</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,277.34</t>
-  </si>
-  <si>
-    <t>3,273.60</t>
-  </si>
-  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,873.41</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,842.49</t>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,379.11</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,173.76</t>
-  </si>
-  <si>
-    <t>2,171.00</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,098.50</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>16,178.15</t>
-  </si>
-  <si>
-    <t>16,170.15</t>
+    <t>6,113.07</t>
+  </si>
+  <si>
+    <t>6,094.43</t>
   </si>
 </sst>
 </file>
@@ -501,13 +489,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>12.26</v>
       </c>
       <c r="E3">
-        <v>41.95</v>
+        <v>48.75</v>
       </c>
       <c r="F3">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,113 +509,113 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>3.74</v>
+        <v>1.18</v>
       </c>
       <c r="E4">
-        <v>18.18</v>
+        <v>9.99</v>
       </c>
       <c r="F4">
-        <v>204</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
+      <c r="B5">
+        <v>732.21</v>
+      </c>
+      <c r="C5">
+        <v>729.67</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="E5">
-        <v>36.1</v>
+        <v>18.03</v>
       </c>
       <c r="F5">
-        <v>205</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>446.87</v>
+      </c>
+      <c r="C6">
+        <v>444.21</v>
       </c>
       <c r="D6">
+        <v>2.66</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>40.95</v>
-      </c>
       <c r="F6">
-        <v>181</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>19.38</v>
+        <v>9.99</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>734.7</v>
+      </c>
+      <c r="C8">
+        <v>734.7</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7.99</v>
+        <v>27.57</v>
       </c>
       <c r="F8">
-        <v>85</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>18.64</v>
       </c>
       <c r="E9">
-        <v>164.55</v>
+        <v>114.33</v>
       </c>
       <c r="F9">
-        <v>929</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-14/2026-09-14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-15/2026-09-15</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,49 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,076.43</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,289.76</t>
+  </si>
+  <si>
+    <t>1,288.96</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,717.09</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,439.80</t>
-  </si>
-  <si>
-    <t>1,427.54</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,380.38</t>
-  </si>
-  <si>
-    <t>1,379.20</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
+    <t>1,587.62</t>
+  </si>
+  <si>
+    <t>1,584.66</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,379.11</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,113.07</t>
-  </si>
-  <si>
-    <t>6,094.43</t>
+    <t>6,936.03</t>
+  </si>
+  <si>
+    <t>6,926.25</t>
   </si>
 </sst>
 </file>
@@ -486,136 +489,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>12.26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>48.75</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
-        <v>9.99</v>
+        <v>34.96</v>
       </c>
       <c r="F4">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>732.21</v>
-      </c>
-      <c r="C5">
-        <v>729.67</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>18.03</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
-        <v>446.87</v>
-      </c>
-      <c r="C6">
-        <v>444.21</v>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>397.35</v>
+      </c>
+      <c r="C7">
+        <v>391.33</v>
       </c>
       <c r="D7">
+        <v>6.02</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>9.99</v>
-      </c>
       <c r="F7">
-        <v>97</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>734.7</v>
+        <v>867.78</v>
       </c>
       <c r="C8">
-        <v>734.7</v>
+        <v>867.78</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>27.57</v>
+        <v>12.19</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>18.64</v>
+        <v>9.78</v>
       </c>
       <c r="E9">
-        <v>114.33</v>
+        <v>56.74</v>
       </c>
       <c r="F9">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
-    <t>multi-venue - Sales Summary - 2026-09-15/2026-09-15</t>
+    <t>multi-venue - Sales Summary - 2026-09-16/2026-09-16</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,49 +34,49 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,223.11</t>
+  </si>
+  <si>
+    <t>1,218.61</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,076.43</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,289.76</t>
-  </si>
-  <si>
-    <t>1,288.96</t>
+    <t>1,664.76</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,746.56</t>
+  </si>
+  <si>
+    <t>1,743.37</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,717.09</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,587.62</t>
-  </si>
-  <si>
-    <t>1,584.66</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,018.32</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,936.03</t>
-  </si>
-  <si>
-    <t>6,926.25</t>
+    <t>6,643.28</t>
+  </si>
+  <si>
+    <t>6,626.99</t>
   </si>
 </sst>
 </file>
@@ -489,116 +489,116 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-9.98</v>
       </c>
       <c r="F3">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34.96</v>
+        <v>24.97</v>
       </c>
       <c r="F4">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>486.6</v>
+      </c>
+      <c r="C5">
+        <v>478</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>503.93</v>
+      </c>
+      <c r="C6">
+        <v>503.93</v>
       </c>
       <c r="D6">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9.59</v>
+        <v>9.19</v>
       </c>
       <c r="F6">
-        <v>109</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>397.35</v>
-      </c>
-      <c r="C7">
-        <v>391.33</v>
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>6.02</v>
+        <v>3.19</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28.77</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="B8">
-        <v>867.78</v>
-      </c>
-      <c r="C8">
-        <v>867.78</v>
+      <c r="C8" t="s">
+        <v>18</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>12.19</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -612,13 +612,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>9.78</v>
+        <v>16.29</v>
       </c>
       <c r="E9">
-        <v>56.74</v>
+        <v>52.95</v>
       </c>
       <c r="F9">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-16/2026-09-16</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-17/2026-09-17</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,19 +34,28 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,010.52</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,223.11</t>
-  </si>
-  <si>
-    <t>1,218.61</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,664.76</t>
+    <t>1,358.23</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,941.93</t>
+  </si>
+  <si>
+    <t>2,936.23</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
@@ -55,28 +64,13 @@
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,746.56</t>
-  </si>
-  <si>
-    <t>1,743.37</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,018.32</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,643.28</t>
-  </si>
-  <si>
-    <t>6,626.99</t>
+    <t>7,421.65</t>
+  </si>
+  <si>
+    <t>7,412.33</t>
   </si>
 </sst>
 </file>
@@ -489,136 +483,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>-9.98</v>
+        <v>8.99</v>
       </c>
       <c r="F3">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>952.35</v>
+      </c>
+      <c r="C4">
+        <v>950.59</v>
       </c>
       <c r="D4">
+        <v>1.76</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>24.97</v>
-      </c>
       <c r="F4">
-        <v>111</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>486.6</v>
-      </c>
-      <c r="C5">
-        <v>478</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
-        <v>503.93</v>
-      </c>
-      <c r="C6">
-        <v>503.93</v>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="E6">
-        <v>9.19</v>
+        <v>28.67</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>16</v>
+      <c r="B7">
+        <v>496.41</v>
+      </c>
+      <c r="C7">
+        <v>495.35</v>
       </c>
       <c r="D7">
-        <v>3.19</v>
+        <v>1.06</v>
       </c>
       <c r="E7">
-        <v>28.77</v>
+        <v>8.85</v>
       </c>
       <c r="F7">
-        <v>114</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>662.21</v>
+      </c>
+      <c r="C8">
+        <v>661.41</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
       <c r="D9">
-        <v>16.29</v>
+        <v>9.32</v>
       </c>
       <c r="E9">
-        <v>52.95</v>
+        <v>54.5</v>
       </c>
       <c r="F9">
-        <v>444</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-17/2026-09-17</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-18/2026-09-18</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,918.48</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,692.93</t>
+  </si>
+  <si>
+    <t>2,681.65</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,010.52</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,358.23</t>
+    <t>1,358.80</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,941.93</t>
-  </si>
-  <si>
-    <t>2,936.23</t>
+    <t>1,979.00</t>
+  </si>
+  <si>
+    <t>1,978.10</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
+    <t>1,247.25</t>
+  </si>
+  <si>
+    <t>1,237.25</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
+    <t>1,354.10</t>
+  </si>
+  <si>
+    <t>1,352.12</t>
+  </si>
+  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,421.65</t>
-  </si>
-  <si>
-    <t>7,412.33</t>
+    <t>10,550.56</t>
+  </si>
+  <si>
+    <t>10,526.40</t>
   </si>
 </sst>
 </file>
@@ -489,130 +507,130 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8.99</v>
+        <v>8.79</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>952.35</v>
-      </c>
-      <c r="C4">
-        <v>950.59</v>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>1.76</v>
+        <v>11.28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="E6">
-        <v>28.67</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>206</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>496.41</v>
-      </c>
-      <c r="C7">
-        <v>495.35</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>662.21</v>
-      </c>
-      <c r="C8">
-        <v>661.41</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0.8</v>
+        <v>1.98</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>9.32</v>
+        <v>24.16</v>
       </c>
       <c r="E9">
-        <v>54.5</v>
+        <v>8.79</v>
       </c>
       <c r="F9">
-        <v>519</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-18/2026-09-18</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-19/2026-09-19</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,101.87</t>
+  </si>
+  <si>
+    <t>4,097.41</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,671.02</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,207.14</t>
+  </si>
+  <si>
+    <t>4,201.73</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,918.48</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,692.93</t>
-  </si>
-  <si>
-    <t>2,681.65</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,358.80</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,979.00</t>
-  </si>
-  <si>
-    <t>1,978.10</t>
+    <t>3,279.09</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,247.25</t>
-  </si>
-  <si>
-    <t>1,237.25</t>
+    <t>3,755.01</t>
+  </si>
+  <si>
+    <t>3,742.26</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,354.10</t>
-  </si>
-  <si>
-    <t>1,352.12</t>
+    <t>2,595.57</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,550.56</t>
-  </si>
-  <si>
-    <t>10,526.40</t>
+    <t>19,609.70</t>
+  </si>
+  <si>
+    <t>19,587.08</t>
+  </si>
+  <si>
+    <t>1,199</t>
   </si>
 </sst>
 </file>
@@ -501,36 +501,36 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="E3">
-        <v>8.79</v>
+        <v>80.9</v>
       </c>
       <c r="F3">
-        <v>116</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>11.28</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>203</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -541,36 +541,36 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35.32</v>
       </c>
       <c r="F5">
-        <v>102</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>67.48</v>
       </c>
       <c r="F6">
-        <v>150</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,13 +584,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>12.75</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>168.6</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,36 +601,36 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36.76</v>
       </c>
       <c r="F8">
-        <v>82</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>22.62</v>
+      </c>
+      <c r="E9">
+        <v>389.06</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="D9">
-        <v>24.16</v>
-      </c>
-      <c r="E9">
-        <v>8.79</v>
-      </c>
-      <c r="F9">
-        <v>726</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-19/2026-09-19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-20/2026-09-20</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,58 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>4,101.87</t>
-  </si>
-  <si>
-    <t>4,097.41</t>
+    <t>3,082.50</t>
+  </si>
+  <si>
+    <t>3,078.20</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,283.65</t>
+  </si>
+  <si>
+    <t>3,275.61</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,671.02</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,207.14</t>
-  </si>
-  <si>
-    <t>4,201.73</t>
+    <t>1,780.21</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,279.09</t>
+    <t>2,395.80</t>
+  </si>
+  <si>
+    <t>2,395.02</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,755.01</t>
-  </si>
-  <si>
-    <t>3,742.26</t>
+    <t>4,108.71</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,595.57</t>
+    <t>1,260.46</t>
+  </si>
+  <si>
+    <t>1,258.74</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>19,609.70</t>
-  </si>
-  <si>
-    <t>19,587.08</t>
-  </si>
-  <si>
-    <t>1,199</t>
+    <t>15,911.33</t>
+  </si>
+  <si>
+    <t>15,896.49</t>
   </si>
 </sst>
 </file>
@@ -504,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.46</v>
+        <v>4.3</v>
       </c>
       <c r="E3">
-        <v>80.9</v>
+        <v>9.99</v>
       </c>
       <c r="F3">
-        <v>275</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,36 +521,36 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>8.04</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>46.95</v>
       </c>
       <c r="F4">
-        <v>118</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35.32</v>
+        <v>38.45</v>
       </c>
       <c r="F5">
-        <v>289</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,36 +561,36 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
+        <v>0.78</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>67.48</v>
-      </c>
       <c r="F6">
-        <v>188</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>168.6</v>
+        <v>35.4</v>
       </c>
       <c r="F7">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,36 +601,36 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E8">
-        <v>36.76</v>
+        <v>19.38</v>
       </c>
       <c r="F8">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>22.62</v>
+        <v>14.84</v>
       </c>
       <c r="E9">
-        <v>389.06</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
+        <v>150.17</v>
+      </c>
+      <c r="F9">
+        <v>989</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-20/2026-09-20</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-21/2026-09-21</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,52 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,082.50</t>
-  </si>
-  <si>
-    <t>3,078.20</t>
+    <t>1,274.05</t>
+  </si>
+  <si>
+    <t>1,271.55</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,283.65</t>
-  </si>
-  <si>
-    <t>3,275.61</t>
+    <t>1,939.12</t>
+  </si>
+  <si>
+    <t>1,937.40</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,780.21</t>
+    <t>1,177.94</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,842.70</t>
+  </si>
+  <si>
+    <t>1,841.71</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,395.80</t>
-  </si>
-  <si>
-    <t>2,395.02</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,108.71</t>
+    <t>1,114.37</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,260.46</t>
-  </si>
-  <si>
-    <t>1,258.74</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>15,911.33</t>
-  </si>
-  <si>
-    <t>15,896.49</t>
+    <t>8,071.11</t>
+  </si>
+  <si>
+    <t>8,062.48</t>
   </si>
 </sst>
 </file>
@@ -504,13 +498,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="E3">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>192</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,13 +518,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>8.04</v>
+        <v>1.72</v>
       </c>
       <c r="E4">
-        <v>46.95</v>
+        <v>28.77</v>
       </c>
       <c r="F4">
-        <v>218</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,10 +541,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>38.45</v>
+        <v>34.96</v>
       </c>
       <c r="F5">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -564,13 +558,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="F6">
-        <v>146</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,50 +581,50 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>35.4</v>
+        <v>15.58</v>
       </c>
       <c r="F7">
-        <v>225</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
+      <c r="B8">
+        <v>722.93</v>
+      </c>
+      <c r="C8">
+        <v>719.51</v>
       </c>
       <c r="D8">
-        <v>1.72</v>
+        <v>3.42</v>
       </c>
       <c r="E8">
-        <v>19.38</v>
+        <v>10.19</v>
       </c>
       <c r="F8">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
       <c r="D9">
-        <v>14.84</v>
+        <v>8.63</v>
       </c>
       <c r="E9">
-        <v>150.17</v>
+        <v>115.19</v>
       </c>
       <c r="F9">
-        <v>989</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-21/2026-09-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-22/2026-09-22</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,274.05</t>
-  </si>
-  <si>
-    <t>1,271.55</t>
+    <t>1,454.44</t>
+  </si>
+  <si>
+    <t>1,445.40</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,883.86</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,939.12</t>
-  </si>
-  <si>
-    <t>1,937.40</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,177.94</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,842.70</t>
-  </si>
-  <si>
-    <t>1,841.71</t>
+    <t>1,768.77</t>
+  </si>
+  <si>
+    <t>1,764.18</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,114.37</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,071.11</t>
-  </si>
-  <si>
-    <t>8,062.48</t>
+    <t>7,099.89</t>
+  </si>
+  <si>
+    <t>7,084.46</t>
   </si>
 </sst>
 </file>
@@ -491,140 +482,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>481.47</v>
+      </c>
+      <c r="C3">
+        <v>481.47</v>
       </c>
       <c r="D3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>1.72</v>
+        <v>9.04</v>
       </c>
       <c r="E4">
-        <v>28.77</v>
+        <v>35.94</v>
       </c>
       <c r="F4">
-        <v>138</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>34.96</v>
+        <v>15.98</v>
       </c>
       <c r="F5">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>0.99</v>
+        <v>4.59</v>
       </c>
       <c r="E6">
-        <v>17.7</v>
+        <v>9.59</v>
       </c>
       <c r="F6">
-        <v>86</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>716.25</v>
+      </c>
+      <c r="C7">
+        <v>715.23</v>
       </c>
       <c r="D7">
+        <v>1.02</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>15.58</v>
-      </c>
       <c r="F7">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>722.93</v>
+        <v>795.1</v>
       </c>
       <c r="C8">
-        <v>719.51</v>
+        <v>794.32</v>
       </c>
       <c r="D8">
-        <v>3.42</v>
+        <v>0.78</v>
       </c>
       <c r="E8">
-        <v>10.19</v>
+        <v>8.79</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>8.63</v>
+        <v>15.43</v>
       </c>
       <c r="E9">
-        <v>115.19</v>
+        <v>70.3</v>
       </c>
       <c r="F9">
-        <v>522</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
-    <t>multi-venue - Sales Summary - 2026-09-22/2026-09-22</t>
+    <t>multi-venue - Sales Summary - 2026-09-23/2026-09-23</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,669.46</t>
+  </si>
+  <si>
+    <t>1,668.56</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,121.69</t>
+  </si>
+  <si>
+    <t>2,111.92</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,454.44</t>
-  </si>
-  <si>
-    <t>1,445.40</t>
-  </si>
-  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,883.86</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,768.77</t>
-  </si>
-  <si>
-    <t>1,764.18</t>
+    <t>1,246.58</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,099.89</t>
-  </si>
-  <si>
-    <t>7,084.46</t>
+    <t>6,782.32</t>
+  </si>
+  <si>
+    <t>6,769.87</t>
   </si>
 </sst>
 </file>
@@ -483,19 +483,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>481.47</v>
+        <v>844.75</v>
       </c>
       <c r="C3">
-        <v>481.47</v>
+        <v>844.75</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8.79</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -509,13 +509,13 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>9.04</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>35.94</v>
+        <v>16.08</v>
       </c>
       <c r="F4">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -526,56 +526,56 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>9.77</v>
       </c>
       <c r="E5">
-        <v>15.98</v>
+        <v>21.77</v>
       </c>
       <c r="F5">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
+      <c r="B6">
+        <v>304.44</v>
+      </c>
+      <c r="C6">
+        <v>302.66</v>
       </c>
       <c r="D6">
-        <v>4.59</v>
+        <v>1.78</v>
       </c>
       <c r="E6">
-        <v>9.59</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>124</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>716.25</v>
-      </c>
-      <c r="C7">
-        <v>715.23</v>
+      <c r="C7" t="s">
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>42.55</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -583,19 +583,19 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>795.1</v>
+        <v>595.4</v>
       </c>
       <c r="C8">
-        <v>794.32</v>
+        <v>595.4</v>
       </c>
       <c r="D8">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8.79</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -609,13 +609,13 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>15.43</v>
+        <v>12.45</v>
       </c>
       <c r="E9">
-        <v>70.3</v>
+        <v>89.19</v>
       </c>
       <c r="F9">
-        <v>490</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
-    <t>multi-venue - Sales Summary - 2026-09-23/2026-09-23</t>
+    <t>multi-venue - Sales Summary - 2026-09-24/2026-09-24</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,43 +37,43 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>1,214.12</t>
+  </si>
+  <si>
+    <t>1,213.24</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,669.46</t>
-  </si>
-  <si>
-    <t>1,668.56</t>
-  </si>
-  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,121.69</t>
-  </si>
-  <si>
-    <t>2,111.92</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
+    <t>1,820.61</t>
+  </si>
+  <si>
+    <t>1,818.29</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,246.58</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,278.15</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,782.32</t>
-  </si>
-  <si>
-    <t>6,769.87</t>
+    <t>6,777.20</t>
+  </si>
+  <si>
+    <t>6,772.83</t>
   </si>
 </sst>
 </file>
@@ -482,120 +482,120 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>844.75</v>
-      </c>
-      <c r="C3">
-        <v>844.75</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="E3">
-        <v>8.79</v>
+        <v>61.13</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="B4">
+        <v>785.32</v>
+      </c>
+      <c r="C4">
+        <v>785.32</v>
+      </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>16.08</v>
+        <v>9.85</v>
       </c>
       <c r="F4">
-        <v>117</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>980.56</v>
+      </c>
+      <c r="C5">
+        <v>980.56</v>
       </c>
       <c r="D5">
-        <v>9.77</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21.77</v>
+        <v>8.99</v>
       </c>
       <c r="F5">
-        <v>139</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
-        <v>304.44</v>
-      </c>
-      <c r="C6">
-        <v>302.66</v>
-      </c>
       <c r="D6">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+      <c r="B7">
+        <v>698.44</v>
+      </c>
+      <c r="C7">
+        <v>697.27</v>
       </c>
       <c r="D7">
+        <v>1.17</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>42.55</v>
-      </c>
       <c r="F7">
-        <v>93</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
-        <v>595.4</v>
-      </c>
-      <c r="C8">
-        <v>595.4</v>
+      <c r="C8" t="s">
+        <v>17</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>29.86</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -609,13 +609,13 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>12.45</v>
+        <v>4.37</v>
       </c>
       <c r="E9">
-        <v>89.19</v>
+        <v>119.42</v>
       </c>
       <c r="F9">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-24/2026-09-24</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-25/2026-09-25</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,049.99</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,868.80</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,540.93</t>
+  </si>
+  <si>
+    <t>1,527.07</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,494.04</t>
+  </si>
+  <si>
+    <t>2,485.36</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,214.12</t>
-  </si>
-  <si>
-    <t>1,213.24</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,820.61</t>
-  </si>
-  <si>
-    <t>1,818.29</t>
+    <t>2,535.87</t>
+  </si>
+  <si>
+    <t>2,533.53</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,278.15</t>
+    <t>1,235.73</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,777.20</t>
-  </si>
-  <si>
-    <t>6,772.83</t>
+    <t>10,725.36</t>
+  </si>
+  <si>
+    <t>10,700.48</t>
   </si>
 </sst>
 </file>
@@ -486,136 +498,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>61.13</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>78</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>785.32</v>
-      </c>
-      <c r="C4">
-        <v>785.32</v>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9.85</v>
+        <v>64.41</v>
       </c>
       <c r="F4">
-        <v>47</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>980.56</v>
-      </c>
-      <c r="C5">
-        <v>980.56</v>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>13.86</v>
       </c>
       <c r="E5">
-        <v>8.99</v>
+        <v>19.4</v>
       </c>
       <c r="F5">
-        <v>68</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>2.32</v>
+        <v>8.68</v>
       </c>
       <c r="E6">
-        <v>9.59</v>
+        <v>62.44</v>
       </c>
       <c r="F6">
-        <v>133</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>698.44</v>
-      </c>
-      <c r="C7">
-        <v>697.27</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>1.17</v>
+        <v>2.34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>66.32</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>29.86</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>4.37</v>
+        <v>24.88</v>
       </c>
       <c r="E9">
-        <v>119.42</v>
+        <v>220.56</v>
       </c>
       <c r="F9">
-        <v>459</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-25/2026-09-25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-26/2026-09-26</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,55 +37,61 @@
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,049.99</t>
+    <t>1,833.43</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,868.80</t>
+    <t>3,337.02</t>
+  </si>
+  <si>
+    <t>3,334.92</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,223.77</t>
+  </si>
+  <si>
+    <t>4,218.83</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,540.93</t>
-  </si>
-  <si>
-    <t>1,527.07</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,494.04</t>
-  </si>
-  <si>
-    <t>2,485.36</t>
+    <t>4,884.63</t>
+  </si>
+  <si>
+    <t>4,878.10</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,864.20</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,535.87</t>
-  </si>
-  <si>
-    <t>2,533.53</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,235.73</t>
+    <t>3,880.21</t>
+  </si>
+  <si>
+    <t>3,879.33</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,725.36</t>
-  </si>
-  <si>
-    <t>10,700.48</t>
+    <t>21,023.26</t>
+  </si>
+  <si>
+    <t>21,008.81</t>
+  </si>
+  <si>
+    <t>1,253</t>
   </si>
 </sst>
 </file>
@@ -504,10 +510,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>11.48</v>
       </c>
       <c r="F3">
-        <v>91</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,76 +524,76 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="E4">
-        <v>64.41</v>
+        <v>24.97</v>
       </c>
       <c r="F4">
-        <v>130</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>13.86</v>
+        <v>4.94</v>
       </c>
       <c r="E5">
-        <v>19.4</v>
+        <v>8.59</v>
       </c>
       <c r="F5">
-        <v>95</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>8.68</v>
+        <v>6.53</v>
       </c>
       <c r="E6">
-        <v>62.44</v>
+        <v>19.54</v>
       </c>
       <c r="F6">
-        <v>165</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>66.32</v>
+        <v>27.57</v>
       </c>
       <c r="F7">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -598,36 +604,36 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>57.73</v>
       </c>
       <c r="F8">
-        <v>68</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>24.88</v>
+        <v>14.45</v>
       </c>
       <c r="E9">
-        <v>220.56</v>
-      </c>
-      <c r="F9">
-        <v>724</v>
+        <v>149.88</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-26/2026-09-26</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-27/2026-09-27</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,465.96</t>
+  </si>
+  <si>
+    <t>3,464.30</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,937.60</t>
+  </si>
+  <si>
+    <t>1,934.78</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,833.43</t>
+    <t>1,489.70</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,195.70</t>
+  </si>
+  <si>
+    <t>3,186.78</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,717.38</t>
+  </si>
+  <si>
+    <t>3,713.68</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,337.02</t>
-  </si>
-  <si>
-    <t>3,334.92</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,223.77</t>
-  </si>
-  <si>
-    <t>4,218.83</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,884.63</t>
-  </si>
-  <si>
-    <t>4,878.10</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,864.20</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,880.21</t>
-  </si>
-  <si>
-    <t>3,879.33</t>
+    <t>2,745.61</t>
+  </si>
+  <si>
+    <t>2,742.91</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>21,023.26</t>
-  </si>
-  <si>
-    <t>21,008.81</t>
-  </si>
-  <si>
-    <t>1,253</t>
+    <t>16,551.95</t>
+  </si>
+  <si>
+    <t>16,532.15</t>
+  </si>
+  <si>
+    <t>1,004</t>
   </si>
 </sst>
 </file>
@@ -504,56 +507,56 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E3">
-        <v>11.48</v>
+        <v>67.12</v>
       </c>
       <c r="F3">
-        <v>136</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="E4">
-        <v>24.97</v>
+        <v>38.76</v>
       </c>
       <c r="F4">
-        <v>222</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8.59</v>
+        <v>9.99</v>
       </c>
       <c r="F5">
-        <v>269</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,13 +570,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>6.53</v>
+        <v>8.92</v>
       </c>
       <c r="E6">
-        <v>19.54</v>
+        <v>19.7</v>
       </c>
       <c r="F6">
-        <v>257</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,56 +587,56 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="E7">
-        <v>27.57</v>
+        <v>49.85</v>
       </c>
       <c r="F7">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>0.88</v>
+        <v>2.7</v>
       </c>
       <c r="E8">
-        <v>57.73</v>
+        <v>16.98</v>
       </c>
       <c r="F8">
-        <v>226</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>14.45</v>
+        <v>19.8</v>
       </c>
       <c r="E9">
-        <v>149.88</v>
+        <v>202.4</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-27/2026-09-27</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-28/2026-09-28</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,855.11</t>
+  </si>
+  <si>
+    <t>1,850.29</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,465.96</t>
-  </si>
-  <si>
-    <t>3,464.30</t>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,062.42</t>
+  </si>
+  <si>
+    <t>1,062.06</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,983.69</t>
+  </si>
+  <si>
+    <t>1,982.80</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,111.99</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,937.60</t>
-  </si>
-  <si>
-    <t>1,934.78</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,489.70</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,195.70</t>
-  </si>
-  <si>
-    <t>3,186.78</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,717.38</t>
-  </si>
-  <si>
-    <t>3,713.68</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,745.61</t>
-  </si>
-  <si>
-    <t>2,742.91</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>16,551.95</t>
-  </si>
-  <si>
-    <t>16,532.15</t>
-  </si>
-  <si>
-    <t>1,004</t>
+    <t>7,532.69</t>
+  </si>
+  <si>
+    <t>7,525.84</t>
   </si>
 </sst>
 </file>
@@ -510,133 +495,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.66</v>
+        <v>4.82</v>
       </c>
       <c r="E3">
-        <v>67.12</v>
+        <v>30.46</v>
       </c>
       <c r="F3">
-        <v>211</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>827.67</v>
+      </c>
+      <c r="C4">
+        <v>826.89</v>
       </c>
       <c r="D4">
-        <v>2.82</v>
+        <v>0.78</v>
       </c>
       <c r="E4">
-        <v>38.76</v>
+        <v>33.76</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="E5">
-        <v>9.99</v>
+        <v>23.97</v>
       </c>
       <c r="F5">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>8.92</v>
+        <v>0.89</v>
       </c>
       <c r="E6">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>182</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>49.85</v>
+        <v>21.47</v>
       </c>
       <c r="F7">
-        <v>216</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>691.81</v>
+      </c>
+      <c r="C8">
+        <v>691.81</v>
       </c>
       <c r="D8">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>16.98</v>
+        <v>19.38</v>
       </c>
       <c r="F8">
-        <v>182</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>19.8</v>
+        <v>6.85</v>
       </c>
       <c r="E9">
-        <v>202.4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
+        <v>129.04</v>
+      </c>
+      <c r="F9">
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-28/2026-09-28</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-29/2026-09-29</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,10 +37,7 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,855.11</t>
-  </si>
-  <si>
-    <t>1,850.29</t>
+    <t>1,946.13</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
@@ -49,25 +46,22 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,062.42</t>
-  </si>
-  <si>
-    <t>1,062.06</t>
+    <t>1,541.02</t>
+  </si>
+  <si>
+    <t>1,537.42</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,983.69</t>
-  </si>
-  <si>
-    <t>1,982.80</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,111.99</t>
+    <t>1,544.87</t>
+  </si>
+  <si>
+    <t>1,543.09</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
@@ -76,10 +70,10 @@
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,532.69</t>
-  </si>
-  <si>
-    <t>7,525.84</t>
+    <t>7,492.54</t>
+  </si>
+  <si>
+    <t>7,487.16</t>
   </si>
 </sst>
 </file>
@@ -492,136 +486,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30.46</v>
+        <v>72.03</v>
       </c>
       <c r="F3">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>827.67</v>
+        <v>750.89</v>
       </c>
       <c r="C4">
-        <v>826.89</v>
+        <v>750.89</v>
       </c>
       <c r="D4">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33.76</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5">
-        <v>0.36</v>
+        <v>3.6</v>
       </c>
       <c r="E5">
-        <v>23.97</v>
+        <v>7.99</v>
       </c>
       <c r="F5">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>941.77</v>
+      </c>
+      <c r="C6">
+        <v>941.77</v>
       </c>
       <c r="D6">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="F6">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="E7">
-        <v>21.47</v>
+        <v>58.09</v>
       </c>
       <c r="F7">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>691.81</v>
+        <v>767.86</v>
       </c>
       <c r="C8">
-        <v>691.81</v>
+        <v>767.86</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>19.38</v>
+        <v>24.12</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
       <c r="D9">
-        <v>6.85</v>
+        <v>5.38</v>
       </c>
       <c r="E9">
-        <v>129.04</v>
+        <v>180.21</v>
       </c>
       <c r="F9">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-29/2026-09-29</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-30/2026-09-30</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,34 +34,40 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,034.47</t>
+  </si>
+  <si>
+    <t>1,032.87</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,946.13</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,541.02</t>
-  </si>
-  <si>
-    <t>1,537.42</t>
+    <t>1,715.64</t>
+  </si>
+  <si>
+    <t>1,712.04</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
+    <t>1,024.93</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,544.87</t>
-  </si>
-  <si>
-    <t>1,543.09</t>
+    <t>1,429.65</t>
+  </si>
+  <si>
+    <t>1,425.48</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
@@ -70,10 +76,10 @@
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,492.54</t>
-  </si>
-  <si>
-    <t>7,487.16</t>
+    <t>6,671.18</t>
+  </si>
+  <si>
+    <t>6,661.81</t>
   </si>
 </sst>
 </file>
@@ -486,33 +492,33 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E3">
-        <v>72.03</v>
+        <v>23.97</v>
       </c>
       <c r="F3">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>750.89</v>
+        <v>710.48</v>
       </c>
       <c r="C4">
-        <v>750.89</v>
+        <v>710.48</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25.37</v>
       </c>
       <c r="F4">
         <v>51</v>
@@ -520,102 +526,102 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>3.6</v>
       </c>
       <c r="E5">
-        <v>7.99</v>
+        <v>17.18</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>941.77</v>
-      </c>
-      <c r="C6">
-        <v>941.77</v>
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>17.98</v>
+        <v>68.94</v>
       </c>
       <c r="F6">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>1.78</v>
+        <v>4.17</v>
       </c>
       <c r="E7">
-        <v>58.09</v>
+        <v>9.85</v>
       </c>
       <c r="F7">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>767.86</v>
+        <v>756.01</v>
       </c>
       <c r="C8">
-        <v>767.86</v>
+        <v>756.01</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>24.12</v>
+        <v>21.18</v>
       </c>
       <c r="F8">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>5.38</v>
+        <v>9.37</v>
       </c>
       <c r="E9">
-        <v>180.21</v>
+        <v>166.49</v>
       </c>
       <c r="F9">
-        <v>513</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
-    <t>multi-venue - Sales Summary - 2026-09-30/2026-09-30</t>
+    <t>multi-venue - Sales Summary - 2026-10-01/2026-10-01</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,52 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,337.78</t>
+  </si>
+  <si>
+    <t>2,331.76</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,034.47</t>
-  </si>
-  <si>
-    <t>1,032.87</t>
+    <t>1,501.70</t>
+  </si>
+  <si>
+    <t>1,500.80</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,043.54</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,267.34</t>
+  </si>
+  <si>
+    <t>1,264.49</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,715.64</t>
-  </si>
-  <si>
-    <t>1,712.04</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,024.93</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,429.65</t>
-  </si>
-  <si>
-    <t>1,425.48</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,671.18</t>
-  </si>
-  <si>
-    <t>6,661.81</t>
+    <t>7,360.32</t>
+  </si>
+  <si>
+    <t>7,350.55</t>
   </si>
 </sst>
 </file>
@@ -495,93 +495,93 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.6</v>
+        <v>6.02</v>
       </c>
       <c r="E3">
-        <v>23.97</v>
+        <v>12.28</v>
       </c>
       <c r="F3">
-        <v>78</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>710.48</v>
-      </c>
-      <c r="C4">
-        <v>710.48</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>25.37</v>
+        <v>24.97</v>
       </c>
       <c r="F4">
-        <v>51</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>17.18</v>
+        <v>16.88</v>
       </c>
       <c r="F5">
-        <v>108</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6">
+        <v>2.85</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>68.94</v>
-      </c>
       <c r="F6">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
         <v>18</v>
       </c>
+      <c r="B7">
+        <v>710.89</v>
+      </c>
+      <c r="C7">
+        <v>710.89</v>
+      </c>
       <c r="D7">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>83</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -589,19 +589,19 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>756.01</v>
+        <v>499.07</v>
       </c>
       <c r="C8">
-        <v>756.01</v>
+        <v>499.07</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>21.18</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -615,13 +615,13 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>9.37</v>
+        <v>9.77</v>
       </c>
       <c r="E9">
-        <v>166.49</v>
+        <v>54.13</v>
       </c>
       <c r="F9">
-        <v>448</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-01/2026-10-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-02/2026-10-02</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,52 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,876.08</t>
+  </si>
+  <si>
+    <t>2,875.20</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,583.26</t>
+  </si>
+  <si>
+    <t>1,582.28</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,207.76</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,337.78</t>
-  </si>
-  <si>
-    <t>2,331.76</t>
+    <t>2,071.00</t>
+  </si>
+  <si>
+    <t>2,068.22</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,278.06</t>
+  </si>
+  <si>
+    <t>1,268.61</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,501.70</t>
-  </si>
-  <si>
-    <t>1,500.80</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,043.54</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,267.34</t>
-  </si>
-  <si>
-    <t>1,264.49</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
+    <t>1,834.91</t>
+  </si>
+  <si>
+    <t>1,834.16</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,360.32</t>
-  </si>
-  <si>
-    <t>7,350.55</t>
+    <t>10,851.07</t>
+  </si>
+  <si>
+    <t>10,836.23</t>
   </si>
 </sst>
 </file>
@@ -495,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.02</v>
+        <v>0.88</v>
       </c>
       <c r="E3">
-        <v>12.28</v>
+        <v>75.81</v>
       </c>
       <c r="F3">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -515,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="E4">
-        <v>24.97</v>
+        <v>44.78</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -538,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>16.88</v>
+        <v>48.84</v>
       </c>
       <c r="F5">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -555,73 +567,73 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="F6">
-        <v>67</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7">
-        <v>710.89</v>
-      </c>
-      <c r="C7">
-        <v>710.89</v>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>9.45</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>20.69</v>
       </c>
       <c r="F7">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8">
-        <v>499.07</v>
-      </c>
-      <c r="C8">
-        <v>499.07</v>
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25.97</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>9.77</v>
+        <v>14.84</v>
       </c>
       <c r="E9">
-        <v>54.13</v>
+        <v>224.68</v>
       </c>
       <c r="F9">
-        <v>500</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-02/2026-10-02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-03/2026-10-03</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,61 +37,61 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,876.08</t>
-  </si>
-  <si>
-    <t>2,875.20</t>
+    <t>3,959.70</t>
+  </si>
+  <si>
+    <t>3,957.16</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,668.31</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,200.91</t>
+  </si>
+  <si>
+    <t>4,194.53</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,583.26</t>
-  </si>
-  <si>
-    <t>1,582.28</t>
+    <t>1,512.19</t>
+  </si>
+  <si>
+    <t>1,511.27</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,207.76</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,071.00</t>
-  </si>
-  <si>
-    <t>2,068.22</t>
+    <t>1,706.55</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,278.06</t>
-  </si>
-  <si>
-    <t>1,268.61</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,834.91</t>
-  </si>
-  <si>
-    <t>1,834.16</t>
+    <t>3,376.64</t>
+  </si>
+  <si>
+    <t>3,374.87</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,851.07</t>
-  </si>
-  <si>
-    <t>10,836.23</t>
+    <t>18,424.30</t>
+  </si>
+  <si>
+    <t>18,412.69</t>
+  </si>
+  <si>
+    <t>1,133</t>
   </si>
 </sst>
 </file>
@@ -507,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.88</v>
+        <v>2.54</v>
       </c>
       <c r="E3">
-        <v>75.81</v>
+        <v>49.65</v>
       </c>
       <c r="F3">
-        <v>185</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,36 +524,36 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>44.78</v>
+        <v>27.91</v>
       </c>
       <c r="F4">
-        <v>82</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="E5">
-        <v>48.84</v>
+        <v>48.44</v>
       </c>
       <c r="F5">
-        <v>98</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,13 +567,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>2.78</v>
+        <v>0.92</v>
       </c>
       <c r="E6">
-        <v>8.59</v>
+        <v>30.57</v>
       </c>
       <c r="F6">
-        <v>151</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,56 +584,56 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>9.45</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>20.69</v>
+        <v>60.83</v>
       </c>
       <c r="F7">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>1.77</v>
       </c>
       <c r="E8">
-        <v>25.97</v>
+        <v>19.54</v>
       </c>
       <c r="F8">
-        <v>137</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>11.61</v>
+      </c>
+      <c r="E9">
+        <v>236.94</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
-      </c>
-      <c r="D9">
-        <v>14.84</v>
-      </c>
-      <c r="E9">
-        <v>224.68</v>
-      </c>
-      <c r="F9">
-        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-03/2026-10-03</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-04/2026-10-04</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,217.24</t>
+  </si>
+  <si>
+    <t>3,211.45</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,959.70</t>
-  </si>
-  <si>
-    <t>3,957.16</t>
+    <t>3,931.50</t>
+  </si>
+  <si>
+    <t>3,929.84</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,668.31</t>
+    <t>3,113.09</t>
+  </si>
+  <si>
+    <t>3,111.39</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,232.16</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,362.49</t>
+  </si>
+  <si>
+    <t>1,359.21</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,200.91</t>
-  </si>
-  <si>
-    <t>4,194.53</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,512.19</t>
-  </si>
-  <si>
-    <t>1,511.27</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,706.55</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,376.64</t>
-  </si>
-  <si>
-    <t>3,374.87</t>
+    <t>3,774.64</t>
+  </si>
+  <si>
+    <t>3,768.46</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>18,424.30</t>
-  </si>
-  <si>
-    <t>18,412.69</t>
-  </si>
-  <si>
-    <t>1,133</t>
+    <t>16,631.12</t>
+  </si>
+  <si>
+    <t>16,612.51</t>
   </si>
 </sst>
 </file>
@@ -507,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.54</v>
+        <v>5.79</v>
       </c>
       <c r="E3">
-        <v>49.65</v>
+        <v>-1</v>
       </c>
       <c r="F3">
-        <v>239</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,56 +524,56 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E4">
-        <v>27.91</v>
+        <v>28.77</v>
       </c>
       <c r="F4">
-        <v>235</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>6.38</v>
+        <v>1.7</v>
       </c>
       <c r="E5">
-        <v>48.44</v>
+        <v>44.95</v>
       </c>
       <c r="F5">
-        <v>266</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>30.57</v>
+        <v>14.97</v>
       </c>
       <c r="F6">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,56 +584,56 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="E7">
-        <v>60.83</v>
+        <v>20.38</v>
       </c>
       <c r="F7">
-        <v>125</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>1.77</v>
+        <v>6.18</v>
       </c>
       <c r="E8">
-        <v>19.54</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>11.61</v>
+        <v>18.61</v>
       </c>
       <c r="E9">
-        <v>236.94</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
+        <v>108.07</v>
+      </c>
+      <c r="F9">
+        <v>953</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-04/2026-10-04</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-05/2026-10-05</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,246.73</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,516.07</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,217.24</t>
-  </si>
-  <si>
-    <t>3,211.45</t>
-  </si>
-  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,931.50</t>
-  </si>
-  <si>
-    <t>3,929.84</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,113.09</t>
-  </si>
-  <si>
-    <t>3,111.39</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,232.16</t>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,035.56</t>
+  </si>
+  <si>
+    <t>2,027.91</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,362.49</t>
-  </si>
-  <si>
-    <t>1,359.21</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,774.64</t>
-  </si>
-  <si>
-    <t>3,768.46</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>16,631.12</t>
-  </si>
-  <si>
-    <t>16,612.51</t>
+    <t>7,033.39</t>
+  </si>
+  <si>
+    <t>7,022.82</t>
   </si>
 </sst>
 </file>
@@ -504,136 +483,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>-1</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>158</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28.77</v>
+        <v>16.98</v>
       </c>
       <c r="F4">
-        <v>179</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>889.89</v>
+      </c>
+      <c r="C5">
+        <v>887.22</v>
       </c>
       <c r="D5">
-        <v>1.7</v>
+        <v>2.67</v>
       </c>
       <c r="E5">
-        <v>44.95</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>205</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>752.46</v>
+      </c>
+      <c r="C6">
+        <v>752.46</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>14.97</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>91</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>3.28</v>
+        <v>7.65</v>
       </c>
       <c r="E7">
-        <v>20.38</v>
+        <v>36.36</v>
       </c>
       <c r="F7">
-        <v>81</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>592.68</v>
+      </c>
+      <c r="C8">
+        <v>592.43</v>
       </c>
       <c r="D8">
-        <v>6.18</v>
+        <v>0.25</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F8">
-        <v>239</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>18.61</v>
+        <v>10.57</v>
       </c>
       <c r="E9">
-        <v>108.07</v>
+        <v>70.52</v>
       </c>
       <c r="F9">
-        <v>953</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-05/2026-10-05</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-06/2026-10-06</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,832.54</t>
+  </si>
+  <si>
+    <t>1,829.04</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,257.47</t>
+  </si>
+  <si>
+    <t>1,253.45</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,822.39</t>
+  </si>
+  <si>
+    <t>1,817.75</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,246.73</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,516.07</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,035.56</t>
-  </si>
-  <si>
-    <t>2,027.91</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,586.02</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,033.39</t>
-  </si>
-  <si>
-    <t>7,022.82</t>
+    <t>7,994.58</t>
+  </si>
+  <si>
+    <t>7,975.15</t>
   </si>
 </sst>
 </file>
@@ -483,136 +492,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>17.98</v>
       </c>
       <c r="F3">
-        <v>99</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="E4">
-        <v>16.98</v>
+        <v>7.79</v>
       </c>
       <c r="F4">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>889.89</v>
+        <v>621.99</v>
       </c>
       <c r="C5">
-        <v>887.22</v>
+        <v>614.72</v>
       </c>
       <c r="D5">
-        <v>2.67</v>
+        <v>7.27</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>752.46</v>
-      </c>
-      <c r="C6">
-        <v>752.46</v>
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17.18</v>
       </c>
       <c r="F6">
-        <v>54</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>874.17</v>
+      </c>
+      <c r="C7">
+        <v>874.17</v>
       </c>
       <c r="D7">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>139</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>592.68</v>
-      </c>
-      <c r="C8">
-        <v>592.43</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>9.19</v>
+        <v>17.98</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>10.57</v>
+        <v>19.43</v>
       </c>
       <c r="E9">
-        <v>70.52</v>
+        <v>60.93</v>
       </c>
       <c r="F9">
-        <v>486</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-06/2026-10-06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-07/2026-10-07</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,52 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,832.54</t>
-  </si>
-  <si>
-    <t>1,829.04</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,257.47</t>
-  </si>
-  <si>
-    <t>1,253.45</t>
+    <t>2,105.00</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,634.89</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,401.61</t>
+  </si>
+  <si>
+    <t>2,399.64</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,822.39</t>
-  </si>
-  <si>
-    <t>1,817.75</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,586.02</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,994.58</t>
-  </si>
-  <si>
-    <t>7,975.15</t>
+    <t>8,129.62</t>
+  </si>
+  <si>
+    <t>8,101.11</t>
   </si>
 </sst>
 </file>
@@ -488,91 +479,91 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>737.19</v>
+      </c>
+      <c r="C3">
+        <v>736.41</v>
       </c>
       <c r="D3">
-        <v>3.5</v>
+        <v>0.78</v>
       </c>
       <c r="E3">
-        <v>17.98</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>129</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7.79</v>
+        <v>17.97</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>621.99</v>
-      </c>
-      <c r="C5">
-        <v>614.72</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25.97</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>4.64</v>
+        <v>1.97</v>
       </c>
       <c r="E6">
-        <v>17.18</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>874.17</v>
+        <v>540</v>
       </c>
       <c r="C7">
-        <v>874.17</v>
+        <v>540</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -581,47 +572,47 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>710.93</v>
+      </c>
+      <c r="C8">
+        <v>685.17</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>25.76</v>
       </c>
       <c r="E8">
-        <v>17.98</v>
+        <v>9.75</v>
       </c>
       <c r="F8">
-        <v>125</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>19.43</v>
+        <v>28.51</v>
       </c>
       <c r="E9">
-        <v>60.93</v>
+        <v>53.69</v>
       </c>
       <c r="F9">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-07/2026-10-07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-08/2026-10-08</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,181.12</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>1,164.22</t>
+  </si>
+  <si>
+    <t>1,162.56</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,481.65</t>
+  </si>
+  <si>
+    <t>2,472.58</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,105.00</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,634.89</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,401.61</t>
-  </si>
-  <si>
-    <t>2,399.64</t>
+    <t>1,898.00</t>
+  </si>
+  <si>
+    <t>1,896.80</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,129.62</t>
-  </si>
-  <si>
-    <t>8,101.11</t>
+    <t>8,498.74</t>
+  </si>
+  <si>
+    <t>8,472.44</t>
   </si>
 </sst>
 </file>
@@ -479,140 +488,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>737.19</v>
-      </c>
-      <c r="C3">
-        <v>736.41</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>15.98</v>
       </c>
       <c r="F3">
-        <v>49</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E4">
-        <v>17.97</v>
+        <v>15.58</v>
       </c>
       <c r="F4">
-        <v>149</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>941.18</v>
+      </c>
+      <c r="C5">
+        <v>927.83</v>
       </c>
       <c r="D5">
+        <v>13.35</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>25.97</v>
-      </c>
       <c r="F5">
-        <v>120</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>1.97</v>
+        <v>9.07</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17.18</v>
       </c>
       <c r="F6">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>540</v>
-      </c>
-      <c r="C7">
-        <v>540</v>
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>52.54</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>710.93</v>
+        <v>832.57</v>
       </c>
       <c r="C8">
-        <v>685.17</v>
+        <v>831.55</v>
       </c>
       <c r="D8">
-        <v>25.76</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>28.51</v>
+        <v>26.3</v>
       </c>
       <c r="E9">
-        <v>53.69</v>
+        <v>101.28</v>
       </c>
       <c r="F9">
-        <v>538</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-08/2026-10-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-09/2026-10-09</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,49 +37,55 @@
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,181.12</t>
+    <t>1,572.77</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,006.10</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,034.18</t>
+  </si>
+  <si>
+    <t>3,029.78</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,217.44</t>
+  </si>
+  <si>
+    <t>1,202.88</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,164.22</t>
-  </si>
-  <si>
-    <t>1,162.56</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,481.65</t>
-  </si>
-  <si>
-    <t>2,472.58</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,898.00</t>
-  </si>
-  <si>
-    <t>1,896.80</t>
+    <t>2,819.40</t>
+  </si>
+  <si>
+    <t>2,815.60</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
+    <t>1,605.30</t>
+  </si>
+  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,498.74</t>
-  </si>
-  <si>
-    <t>8,472.44</t>
+    <t>12,255.19</t>
+  </si>
+  <si>
+    <t>12,232.43</t>
   </si>
 </sst>
 </file>
@@ -498,10 +504,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15.98</v>
+        <v>32.86</v>
       </c>
       <c r="F3">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -512,116 +518,116 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>15.58</v>
+        <v>32.96</v>
       </c>
       <c r="F4">
-        <v>81</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5">
-        <v>941.18</v>
-      </c>
-      <c r="C5">
-        <v>927.83</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>13.35</v>
+        <v>4.4</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="F5">
-        <v>59</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>9.07</v>
+        <v>14.56</v>
       </c>
       <c r="E6">
-        <v>17.18</v>
+        <v>18.7</v>
       </c>
       <c r="F6">
-        <v>172</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="E7">
-        <v>52.54</v>
+        <v>40.15</v>
       </c>
       <c r="F7">
-        <v>143</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8">
-        <v>832.57</v>
-      </c>
-      <c r="C8">
-        <v>831.55</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>40.19</v>
       </c>
       <c r="F8">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>26.3</v>
+        <v>22.76</v>
       </c>
       <c r="E9">
-        <v>101.28</v>
+        <v>192.63</v>
       </c>
       <c r="F9">
-        <v>615</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-09/2026-10-09</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-10/2026-10-10</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,154.46</t>
+  </si>
+  <si>
+    <t>4,152.06</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,572.77</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,006.10</t>
+    <t>1,818.83</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,412.90</t>
+  </si>
+  <si>
+    <t>4,404.50</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>4,395.83</t>
+  </si>
+  <si>
+    <t>4,393.39</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,034.18</t>
-  </si>
-  <si>
-    <t>3,029.78</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,217.44</t>
-  </si>
-  <si>
-    <t>1,202.88</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,819.40</t>
-  </si>
-  <si>
-    <t>2,815.60</t>
+    <t>4,404.06</t>
+  </si>
+  <si>
+    <t>4,390.98</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,605.30</t>
+    <t>1,894.06</t>
+  </si>
+  <si>
+    <t>1,893.04</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>12,255.19</t>
-  </si>
-  <si>
-    <t>12,232.43</t>
+    <t>21,080.14</t>
+  </si>
+  <si>
+    <t>21,052.80</t>
+  </si>
+  <si>
+    <t>1,282</t>
   </si>
 </sst>
 </file>
@@ -498,136 +507,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="E3">
-        <v>32.86</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>125</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.96</v>
+        <v>25.07</v>
       </c>
       <c r="F4">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="E5">
-        <v>27.77</v>
+        <v>56.2</v>
       </c>
       <c r="F5">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>14.56</v>
+        <v>2.44</v>
       </c>
       <c r="E6">
-        <v>18.7</v>
+        <v>65.92</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>3.8</v>
+        <v>13.08</v>
       </c>
       <c r="E7">
-        <v>40.15</v>
+        <v>28.77</v>
       </c>
       <c r="F7">
-        <v>170</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8">
+        <v>1.02</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>40.19</v>
-      </c>
       <c r="F8">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>22.76</v>
+        <v>27.34</v>
       </c>
       <c r="E9">
-        <v>192.63</v>
-      </c>
-      <c r="F9">
-        <v>792</v>
+        <v>183.95</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-10/2026-10-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-11/2026-10-11</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>5,435.54</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>4,154.46</t>
-  </si>
-  <si>
-    <t>4,152.06</t>
+    <t>3,616.90</t>
+  </si>
+  <si>
+    <t>3,615.20</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,700.20</t>
+  </si>
+  <si>
+    <t>4,693.11</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,526.38</t>
+  </si>
+  <si>
+    <t>3,524.82</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,818.83</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,412.90</t>
-  </si>
-  <si>
-    <t>4,404.50</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>4,395.83</t>
-  </si>
-  <si>
-    <t>4,393.39</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,404.06</t>
-  </si>
-  <si>
-    <t>4,390.98</t>
+    <t>1,425.32</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,894.06</t>
-  </si>
-  <si>
-    <t>1,893.04</t>
+    <t>1,847.35</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>21,080.14</t>
-  </si>
-  <si>
-    <t>21,052.80</t>
-  </si>
-  <si>
-    <t>1,282</t>
+    <t>20,551.69</t>
+  </si>
+  <si>
+    <t>20,541.34</t>
+  </si>
+  <si>
+    <t>1,202</t>
   </si>
 </sst>
 </file>
@@ -507,13 +501,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>256</v>
@@ -521,22 +515,22 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E4">
-        <v>25.07</v>
+        <v>24.97</v>
       </c>
       <c r="F4">
-        <v>141</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,13 +544,13 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>8.4</v>
+        <v>7.09</v>
       </c>
       <c r="E5">
-        <v>56.2</v>
+        <v>41.85</v>
       </c>
       <c r="F5">
-        <v>265</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -570,13 +564,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="E6">
-        <v>65.92</v>
+        <v>252.9</v>
       </c>
       <c r="F6">
-        <v>240</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,56 +581,56 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28.77</v>
+        <v>23.97</v>
       </c>
       <c r="F7">
-        <v>275</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="F8">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9">
+        <v>10.35</v>
+      </c>
+      <c r="E9">
+        <v>395.67</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>27.34</v>
-      </c>
-      <c r="E9">
-        <v>183.95</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-11/2026-10-11</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-12/2026-10-12</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,452.93</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,365.57</t>
+  </si>
+  <si>
+    <t>3,360.49</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>5,435.54</t>
+    <t>3,170.48</t>
+  </si>
+  <si>
+    <t>3,160.11</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,616.90</t>
-  </si>
-  <si>
-    <t>3,615.20</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,700.20</t>
-  </si>
-  <si>
-    <t>4,693.11</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,526.38</t>
-  </si>
-  <si>
-    <t>3,524.82</t>
+    <t>2,206.68</t>
+  </si>
+  <si>
+    <t>2,206.18</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,425.32</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,847.35</t>
+    <t>1,798.89</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>20,551.69</t>
-  </si>
-  <si>
-    <t>20,541.34</t>
-  </si>
-  <si>
-    <t>1,202</t>
+    <t>12,695.24</t>
+  </si>
+  <si>
+    <t>12,679.29</t>
   </si>
 </sst>
 </file>
@@ -497,140 +491,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="B3">
+        <v>700.69</v>
+      </c>
+      <c r="C3">
+        <v>700.69</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>22.99</v>
       </c>
       <c r="F3">
-        <v>256</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24.97</v>
+        <v>3.6</v>
       </c>
       <c r="F4">
-        <v>212</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5">
-        <v>7.09</v>
+        <v>5.08</v>
       </c>
       <c r="E5">
-        <v>41.85</v>
+        <v>38.36</v>
       </c>
       <c r="F5">
-        <v>300</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>10.37</v>
       </c>
       <c r="E6">
-        <v>252.9</v>
+        <v>19.4</v>
       </c>
       <c r="F6">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E7">
-        <v>23.97</v>
+        <v>3.59</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1.98</v>
+        <v>57.93</v>
       </c>
       <c r="F8">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9">
-        <v>10.35</v>
+        <v>15.95</v>
       </c>
       <c r="E9">
-        <v>395.67</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
+        <v>145.87</v>
+      </c>
+      <c r="F9">
+        <v>810</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-12/2026-10-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-13/2026-10-13</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,216.25</t>
+  </si>
+  <si>
+    <t>2,210.57</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,225.35</t>
+  </si>
+  <si>
+    <t>1,222.95</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,235.69</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,452.93</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,365.57</t>
-  </si>
-  <si>
-    <t>3,360.49</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,170.48</t>
-  </si>
-  <si>
-    <t>3,160.11</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,206.68</t>
-  </si>
-  <si>
-    <t>2,206.18</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,798.89</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>12,695.24</t>
-  </si>
-  <si>
-    <t>12,679.29</t>
+    <t>7,273.19</t>
+  </si>
+  <si>
+    <t>7,258.86</t>
   </si>
 </sst>
 </file>
@@ -491,140 +482,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>700.69</v>
-      </c>
-      <c r="C3">
-        <v>700.69</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="E3">
-        <v>22.99</v>
+        <v>8.59</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>991.5</v>
+      </c>
+      <c r="C4">
+        <v>988.38</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="E4">
-        <v>3.6</v>
+        <v>6.98</v>
       </c>
       <c r="F4">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
+      <c r="B5">
+        <v>873.51</v>
+      </c>
+      <c r="C5">
+        <v>870.38</v>
       </c>
       <c r="D5">
-        <v>5.08</v>
+        <v>3.13</v>
       </c>
       <c r="E5">
-        <v>38.36</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>218</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
       <c r="D6">
-        <v>10.37</v>
+        <v>2.4</v>
       </c>
       <c r="E6">
-        <v>19.4</v>
+        <v>19.98</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>3.59</v>
+        <v>8.99</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>730.89</v>
+      </c>
+      <c r="C8">
+        <v>730.89</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>57.93</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>133</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>15.95</v>
+        <v>14.33</v>
       </c>
       <c r="E9">
-        <v>145.87</v>
+        <v>44.54</v>
       </c>
       <c r="F9">
-        <v>810</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-13/2026-10-13</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-14/2026-10-14</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,577.00</t>
+  </si>
+  <si>
+    <t>1,575.55</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,350.64</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,216.25</t>
-  </si>
-  <si>
-    <t>2,210.57</t>
+    <t>1,733.63</t>
+  </si>
+  <si>
+    <t>1,730.85</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,015.90</t>
+  </si>
+  <si>
+    <t>1,013.86</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,225.35</t>
-  </si>
-  <si>
-    <t>1,222.95</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,235.69</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,273.19</t>
-  </si>
-  <si>
-    <t>7,258.86</t>
+    <t>7,314.70</t>
+  </si>
+  <si>
+    <t>7,295.65</t>
   </si>
 </sst>
 </file>
@@ -489,133 +495,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5.68</v>
+        <v>1.45</v>
       </c>
       <c r="E3">
-        <v>8.59</v>
+        <v>69.92</v>
       </c>
       <c r="F3">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>991.5</v>
-      </c>
-      <c r="C4">
-        <v>988.38</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6.98</v>
+        <v>16.98</v>
       </c>
       <c r="F4">
-        <v>62</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>873.51</v>
-      </c>
-      <c r="C5">
-        <v>870.38</v>
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>948.21</v>
+      </c>
+      <c r="C6">
+        <v>948.21</v>
       </c>
       <c r="D6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19.98</v>
+        <v>7.79</v>
       </c>
       <c r="F6">
-        <v>82</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="E7">
-        <v>8.99</v>
+        <v>0.3</v>
       </c>
       <c r="F7">
-        <v>95</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>730.89</v>
+        <v>689.32</v>
       </c>
       <c r="C8">
-        <v>730.89</v>
+        <v>676.54</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>12.78</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>14.33</v>
+        <v>19.05</v>
       </c>
       <c r="E9">
-        <v>44.54</v>
+        <v>113.17</v>
       </c>
       <c r="F9">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-14/2026-10-14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-15/2026-10-15</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,49 +37,46 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,577.00</t>
-  </si>
-  <si>
-    <t>1,575.55</t>
+    <t>1,646.14</t>
+  </si>
+  <si>
+    <t>1,641.66</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,350.64</t>
+    <t>1,310.03</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,733.63</t>
-  </si>
-  <si>
-    <t>1,730.85</t>
+    <t>2,144.86</t>
+  </si>
+  <si>
+    <t>2,137.52</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>1,187.02</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,015.90</t>
-  </si>
-  <si>
-    <t>1,013.86</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,314.70</t>
-  </si>
-  <si>
-    <t>7,295.65</t>
+    <t>7,634.84</t>
+  </si>
+  <si>
+    <t>7,619.01</t>
   </si>
 </sst>
 </file>
@@ -495,13 +492,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.45</v>
+        <v>4.48</v>
       </c>
       <c r="E3">
-        <v>69.92</v>
+        <v>44.44</v>
       </c>
       <c r="F3">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>16.98</v>
+        <v>15.98</v>
       </c>
       <c r="F4">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,13 +532,13 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>2.78</v>
+        <v>7.34</v>
       </c>
       <c r="E5">
-        <v>18.18</v>
+        <v>39.85</v>
       </c>
       <c r="F5">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -549,19 +546,19 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>948.21</v>
+        <v>556.47</v>
       </c>
       <c r="C6">
-        <v>948.21</v>
+        <v>552.46</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="E6">
-        <v>7.79</v>
+        <v>8.85</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -572,56 +569,56 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.3</v>
+        <v>24.08</v>
       </c>
       <c r="F7">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>689.32</v>
+        <v>790.32</v>
       </c>
       <c r="C8">
-        <v>676.54</v>
+        <v>790.32</v>
       </c>
       <c r="D8">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36.06</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
       <c r="D9">
-        <v>19.05</v>
+        <v>15.83</v>
       </c>
       <c r="E9">
-        <v>113.17</v>
+        <v>169.26</v>
       </c>
       <c r="F9">
-        <v>496</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-15/2026-10-15</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-16/2026-10-16</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,46 +37,58 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,646.14</t>
-  </si>
-  <si>
-    <t>1,641.66</t>
+    <t>2,438.80</t>
+  </si>
+  <si>
+    <t>2,435.00</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,754.03</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,340.76</t>
+  </si>
+  <si>
+    <t>2,332.36</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,310.03</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,144.86</t>
-  </si>
-  <si>
-    <t>2,137.52</t>
+    <t>1,394.23</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,286.79</t>
+  </si>
+  <si>
+    <t>1,282.99</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,187.02</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,671.84</t>
+  </si>
+  <si>
+    <t>1,654.58</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,634.84</t>
-  </si>
-  <si>
-    <t>7,619.01</t>
+    <t>11,886.45</t>
+  </si>
+  <si>
+    <t>11,853.19</t>
   </si>
 </sst>
 </file>
@@ -492,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="E3">
-        <v>44.44</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>118</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -515,10 +527,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15.98</v>
+        <v>76.91</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -532,93 +544,93 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>7.34</v>
+        <v>8.4</v>
       </c>
       <c r="E5">
-        <v>39.85</v>
+        <v>30.77</v>
       </c>
       <c r="F5">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
-        <v>556.47</v>
-      </c>
-      <c r="C6">
-        <v>552.46</v>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>8.85</v>
+        <v>8.59</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="E7">
-        <v>24.08</v>
+        <v>34.99</v>
       </c>
       <c r="F7">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>790.32</v>
-      </c>
-      <c r="C8">
-        <v>790.32</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
       </c>
       <c r="D8">
+        <v>17.26</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>36.06</v>
-      </c>
       <c r="F8">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>15.83</v>
+        <v>33.26</v>
       </c>
       <c r="E9">
-        <v>169.26</v>
+        <v>159.25</v>
       </c>
       <c r="F9">
-        <v>549</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-16/2026-10-16</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-17/2026-10-17</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,660.01</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,438.80</t>
-  </si>
-  <si>
-    <t>2,435.00</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,754.03</t>
+    <t>4,325.76</t>
+  </si>
+  <si>
+    <t>4,321.16</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,340.76</t>
-  </si>
-  <si>
-    <t>2,332.36</t>
+    <t>4,045.54</t>
+  </si>
+  <si>
+    <t>4,031.28</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,394.23</t>
+    <t>1,217.14</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,286.79</t>
-  </si>
-  <si>
-    <t>1,282.99</t>
+    <t>1,682.03</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,671.84</t>
-  </si>
-  <si>
-    <t>1,654.58</t>
+    <t>4,577.20</t>
+  </si>
+  <si>
+    <t>4,560.83</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>11,886.45</t>
-  </si>
-  <si>
-    <t>11,853.19</t>
+    <t>18,507.68</t>
+  </si>
+  <si>
+    <t>18,472.45</t>
+  </si>
+  <si>
+    <t>1,119</t>
   </si>
 </sst>
 </file>
@@ -501,36 +501,36 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>200.17</v>
       </c>
       <c r="F3">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="E4">
-        <v>76.91</v>
+        <v>32.96</v>
       </c>
       <c r="F4">
-        <v>176</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,13 +544,13 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>8.4</v>
+        <v>14.26</v>
       </c>
       <c r="E5">
-        <v>30.77</v>
+        <v>86.61</v>
       </c>
       <c r="F5">
-        <v>176</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8.59</v>
+        <v>48.94</v>
       </c>
       <c r="F6">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -581,56 +581,56 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>34.99</v>
+        <v>22.99</v>
       </c>
       <c r="F7">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8">
-        <v>17.26</v>
+        <v>16.37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>70.9</v>
       </c>
       <c r="F8">
-        <v>96</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>35.23</v>
+      </c>
+      <c r="E9">
+        <v>462.57</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="D9">
-        <v>33.26</v>
-      </c>
-      <c r="E9">
-        <v>159.25</v>
-      </c>
-      <c r="F9">
-        <v>798</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
-    <t>multi-venue - Sales Summary - 2026-10-17/2026-10-17</t>
+    <t>multi-venue - Sales Summary - 2026-10-18/2026-10-18</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,928.46</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,660.01</t>
+    <t>3,887.80</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>4,325.76</t>
-  </si>
-  <si>
-    <t>4,321.16</t>
+    <t>3,294.57</t>
+  </si>
+  <si>
+    <t>3,293.02</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,336.18</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,879.38</t>
+  </si>
+  <si>
+    <t>2,877.26</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,045.54</t>
-  </si>
-  <si>
-    <t>4,031.28</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,217.14</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,682.03</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,577.20</t>
-  </si>
-  <si>
-    <t>4,560.83</t>
+    <t>3,985.70</t>
+  </si>
+  <si>
+    <t>3,981.76</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>18,507.68</t>
-  </si>
-  <si>
-    <t>18,472.45</t>
-  </si>
-  <si>
-    <t>1,119</t>
+    <t>17,312.09</t>
+  </si>
+  <si>
+    <t>17,304.48</t>
+  </si>
+  <si>
+    <t>1,065</t>
   </si>
 </sst>
 </file>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>200.17</v>
+        <v>11.69</v>
       </c>
       <c r="F3">
-        <v>147</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,76 +521,76 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32.96</v>
+        <v>82.1</v>
       </c>
       <c r="F4">
-        <v>258</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5">
-        <v>14.26</v>
+        <v>1.55</v>
       </c>
       <c r="E5">
-        <v>86.61</v>
+        <v>59.93</v>
       </c>
       <c r="F5">
-        <v>269</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>48.94</v>
+        <v>15.98</v>
       </c>
       <c r="F6">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
+        <v>2.12</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>22.99</v>
-      </c>
       <c r="F7">
-        <v>90</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,13 +604,13 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>16.37</v>
+        <v>3.94</v>
       </c>
       <c r="E8">
-        <v>70.9</v>
+        <v>92.4</v>
       </c>
       <c r="F8">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,10 +624,10 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>35.23</v>
+        <v>7.61</v>
       </c>
       <c r="E9">
-        <v>462.57</v>
+        <v>262.1</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-18/2026-10-18</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-19/2026-10-19</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,43 @@
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,928.46</t>
-  </si>
-  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,887.80</t>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,932.52</t>
+  </si>
+  <si>
+    <t>1,926.66</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,272.14</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,294.57</t>
-  </si>
-  <si>
-    <t>3,293.02</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,336.18</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,879.38</t>
-  </si>
-  <si>
-    <t>2,877.26</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,985.70</t>
-  </si>
-  <si>
-    <t>3,981.76</t>
+    <t>1,820.68</t>
+  </si>
+  <si>
+    <t>1,820.33</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>17,312.09</t>
-  </si>
-  <si>
-    <t>17,304.48</t>
-  </si>
-  <si>
-    <t>1,065</t>
+    <t>7,385.84</t>
+  </si>
+  <si>
+    <t>7,373.47</t>
   </si>
 </sst>
 </file>
@@ -497,140 +482,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="B3">
+        <v>923.65</v>
+      </c>
+      <c r="C3">
+        <v>921.61</v>
       </c>
       <c r="D3">
+        <v>2.04</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>11.69</v>
-      </c>
       <c r="F3">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>842.23</v>
+      </c>
+      <c r="C4">
+        <v>842.23</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>82.1</v>
+        <v>16.58</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5">
-        <v>1.55</v>
+        <v>5.86</v>
       </c>
       <c r="E5">
-        <v>59.93</v>
+        <v>25.67</v>
       </c>
       <c r="F5">
-        <v>197</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>15.98</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>594.62</v>
+      </c>
+      <c r="C7">
+        <v>590.5</v>
       </c>
       <c r="D7">
-        <v>2.12</v>
+        <v>4.12</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>178</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>3.94</v>
+        <v>0.35</v>
       </c>
       <c r="E8">
-        <v>92.4</v>
+        <v>7.69</v>
       </c>
       <c r="F8">
-        <v>250</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>7.61</v>
+        <v>12.37</v>
       </c>
       <c r="E9">
-        <v>262.1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
+        <v>49.94</v>
+      </c>
+      <c r="F9">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-19/2026-10-19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-20/2026-10-20</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,104.37</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,621.86</t>
+  </si>
+  <si>
+    <t>1,609.35</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,338.01</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,932.52</t>
-  </si>
-  <si>
-    <t>1,926.66</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,272.14</t>
-  </si>
-  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,820.68</t>
-  </si>
-  <si>
-    <t>1,820.33</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,385.84</t>
-  </si>
-  <si>
-    <t>7,373.47</t>
+    <t>6,351.49</t>
+  </si>
+  <si>
+    <t>6,327.96</t>
   </si>
 </sst>
 </file>
@@ -482,140 +479,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>923.65</v>
-      </c>
-      <c r="C3">
-        <v>921.61</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="F3">
-        <v>62</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>842.23</v>
-      </c>
-      <c r="C4">
-        <v>842.23</v>
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
+        <v>12.51</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>16.58</v>
-      </c>
       <c r="F4">
-        <v>54</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>947.01</v>
+      </c>
+      <c r="C5">
+        <v>947.01</v>
       </c>
       <c r="D5">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25.67</v>
+        <v>23.37</v>
       </c>
       <c r="F5">
-        <v>127</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>50.54</v>
       </c>
       <c r="F6">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>594.62</v>
+        <v>861.94</v>
       </c>
       <c r="C7">
-        <v>590.5</v>
+        <v>861.94</v>
       </c>
       <c r="D7">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
+      <c r="B8">
+        <v>478.3</v>
+      </c>
+      <c r="C8">
+        <v>467.28</v>
       </c>
       <c r="D8">
-        <v>0.35</v>
+        <v>11.02</v>
       </c>
       <c r="E8">
-        <v>7.69</v>
+        <v>53.57</v>
       </c>
       <c r="F8">
-        <v>118</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
       <c r="D9">
-        <v>12.37</v>
+        <v>23.53</v>
       </c>
       <c r="E9">
-        <v>49.94</v>
+        <v>145.26</v>
       </c>
       <c r="F9">
-        <v>494</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
-    <t>multi-venue - Sales Summary - 2026-10-20/2026-10-20</t>
+    <t>multi-venue - Sales Summary - 2026-10-21/2026-10-21</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,719.53</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,104.37</t>
+    <t>1,162.65</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,621.86</t>
-  </si>
-  <si>
-    <t>1,609.35</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,338.01</t>
+    <t>1,085.62</t>
+  </si>
+  <si>
+    <t>1,080.62</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,351.49</t>
-  </si>
-  <si>
-    <t>6,327.96</t>
+    <t>6,455.12</t>
+  </si>
+  <si>
+    <t>6,445.38</t>
   </si>
 </sst>
 </file>
@@ -489,70 +489,70 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8.59</v>
+        <v>57.93</v>
       </c>
       <c r="F3">
-        <v>86</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="B4">
+        <v>649.07</v>
+      </c>
+      <c r="C4">
+        <v>649.07</v>
       </c>
       <c r="D4">
-        <v>12.51</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="F4">
-        <v>114</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>947.01</v>
-      </c>
-      <c r="C5">
-        <v>947.01</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>50.54</v>
+        <v>9.59</v>
       </c>
       <c r="F6">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -560,19 +560,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>861.94</v>
+        <v>977.59</v>
       </c>
       <c r="C7">
-        <v>861.94</v>
+        <v>972.85</v>
       </c>
       <c r="D7">
+        <v>4.74</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>9.19</v>
-      </c>
       <c r="F7">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -580,19 +580,19 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>478.3</v>
+        <v>860.66</v>
       </c>
       <c r="C8">
-        <v>467.28</v>
+        <v>860.66</v>
       </c>
       <c r="D8">
-        <v>11.02</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>53.57</v>
+        <v>1.5</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -606,13 +606,13 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>23.53</v>
+        <v>9.74</v>
       </c>
       <c r="E9">
-        <v>145.26</v>
+        <v>84.6</v>
       </c>
       <c r="F9">
-        <v>448</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-21/2026-10-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-22/2026-10-22</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,40 +37,46 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,719.53</t>
+    <t>1,447.06</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,846.82</t>
+  </si>
+  <si>
+    <t>1,841.82</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,461.70</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,162.65</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,085.62</t>
-  </si>
-  <si>
-    <t>1,080.62</t>
+    <t>1,177.53</t>
+  </si>
+  <si>
+    <t>1,176.65</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,455.12</t>
-  </si>
-  <si>
-    <t>6,445.38</t>
+    <t>7,165.19</t>
+  </si>
+  <si>
+    <t>7,157.47</t>
   </si>
 </sst>
 </file>
@@ -489,10 +495,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>57.93</v>
+        <v>16.98</v>
       </c>
       <c r="F3">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -500,19 +506,19 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>649.07</v>
+        <v>597.06</v>
       </c>
       <c r="C4">
-        <v>649.07</v>
+        <v>595.22</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="E4">
-        <v>15.58</v>
+        <v>10.19</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -523,96 +529,96 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9.59</v>
+        <v>47.94</v>
       </c>
       <c r="F6">
-        <v>86</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7">
-        <v>977.59</v>
-      </c>
-      <c r="C7">
-        <v>972.85</v>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>4.74</v>
+        <v>0.88</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>7.79</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>860.66</v>
+        <v>635.02</v>
       </c>
       <c r="C8">
-        <v>860.66</v>
+        <v>635.02</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>9.74</v>
+        <v>7.72</v>
       </c>
       <c r="E9">
-        <v>84.6</v>
+        <v>82.9</v>
       </c>
       <c r="F9">
-        <v>485</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-22/2026-10-22</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-23/2026-10-23</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,49 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,007.15</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,220.33</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,374.49</t>
+  </si>
+  <si>
+    <t>2,368.30</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,149.54</t>
+  </si>
+  <si>
+    <t>1,148.52</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,959.23</t>
+  </si>
+  <si>
+    <t>2,953.95</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,447.06</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,846.82</t>
-  </si>
-  <si>
-    <t>1,841.82</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,461.70</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,177.53</t>
-  </si>
-  <si>
-    <t>1,176.65</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
+    <t>1,987.34</t>
+  </si>
+  <si>
+    <t>1,985.49</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,165.19</t>
-  </si>
-  <si>
-    <t>7,157.47</t>
+    <t>10,698.08</t>
+  </si>
+  <si>
+    <t>10,670.70</t>
   </si>
 </sst>
 </file>
@@ -488,137 +500,137 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>994.11</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>13.04</v>
       </c>
       <c r="E3">
-        <v>16.98</v>
+        <v>8.85</v>
       </c>
       <c r="F3">
-        <v>115</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>597.06</v>
-      </c>
-      <c r="C4">
-        <v>595.22</v>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10.19</v>
+        <v>69.71</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6.19</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>129</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
+        <v>1.02</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>47.94</v>
-      </c>
       <c r="F6">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0.88</v>
+        <v>5.28</v>
       </c>
       <c r="E7">
-        <v>7.79</v>
+        <v>66.72</v>
       </c>
       <c r="F7">
-        <v>74</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>635.02</v>
-      </c>
-      <c r="C8">
-        <v>635.02</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25.27</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>7.72</v>
+        <v>27.38</v>
       </c>
       <c r="E9">
-        <v>82.9</v>
+        <v>170.55</v>
       </c>
       <c r="F9">
-        <v>517</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-23/2026-10-23</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-24/2026-10-24</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,987.42</t>
+  </si>
+  <si>
+    <t>3,982.65</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,753.50</t>
+  </si>
+  <si>
+    <t>3,750.90</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,539.09</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>1,007.15</t>
+    <t>4,351.08</t>
+  </si>
+  <si>
+    <t>4,344.14</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,220.33</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,374.49</t>
-  </si>
-  <si>
-    <t>2,368.30</t>
+    <t>1,570.93</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,149.54</t>
-  </si>
-  <si>
-    <t>1,148.52</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,959.23</t>
-  </si>
-  <si>
-    <t>2,953.95</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,987.34</t>
-  </si>
-  <si>
-    <t>1,985.49</t>
+    <t>2,048.26</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,698.08</t>
-  </si>
-  <si>
-    <t>10,670.70</t>
+    <t>19,250.28</t>
+  </si>
+  <si>
+    <t>19,235.97</t>
+  </si>
+  <si>
+    <t>1,180</t>
   </si>
 </sst>
 </file>
@@ -500,97 +500,97 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>994.11</v>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>13.04</v>
+        <v>4.77</v>
       </c>
       <c r="E3">
-        <v>8.85</v>
+        <v>83.25</v>
       </c>
       <c r="F3">
-        <v>59</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E4">
-        <v>69.71</v>
+        <v>120.46</v>
       </c>
       <c r="F4">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>76.11</v>
       </c>
       <c r="F5">
-        <v>150</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>6.94</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>120.25</v>
       </c>
       <c r="F6">
-        <v>70</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>66.72</v>
+        <v>16.58</v>
       </c>
       <c r="F7">
-        <v>189</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,36 +601,36 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>25.27</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>137</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>14.31</v>
+      </c>
+      <c r="E9">
+        <v>416.65</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="D9">
-        <v>27.38</v>
-      </c>
-      <c r="E9">
-        <v>170.55</v>
-      </c>
-      <c r="F9">
-        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-24/2026-10-24</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-25/2026-10-25</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,549.18</t>
+  </si>
+  <si>
+    <t>2,544.79</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,255.61</t>
+  </si>
+  <si>
+    <t>3,252.11</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,838.87</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,987.42</t>
-  </si>
-  <si>
-    <t>3,982.65</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,753.50</t>
-  </si>
-  <si>
-    <t>3,750.90</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,539.09</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,351.08</t>
-  </si>
-  <si>
-    <t>4,344.14</t>
+    <t>3,676.32</t>
+  </si>
+  <si>
+    <t>3,667.92</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,570.93</t>
+    <t>1,419.04</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,048.26</t>
+    <t>1,222.55</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>19,250.28</t>
-  </si>
-  <si>
-    <t>19,235.97</t>
-  </si>
-  <si>
-    <t>1,180</t>
+    <t>14,961.57</t>
+  </si>
+  <si>
+    <t>14,945.28</t>
   </si>
 </sst>
 </file>
@@ -504,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.77</v>
+        <v>4.39</v>
       </c>
       <c r="E3">
-        <v>83.25</v>
+        <v>31.16</v>
       </c>
       <c r="F3">
-        <v>244</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,13 +521,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="E4">
-        <v>120.46</v>
+        <v>159.6</v>
       </c>
       <c r="F4">
-        <v>252</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>76.11</v>
+        <v>36.1</v>
       </c>
       <c r="F5">
-        <v>233</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -564,13 +561,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>6.94</v>
+        <v>8.4</v>
       </c>
       <c r="E6">
-        <v>120.25</v>
+        <v>37.36</v>
       </c>
       <c r="F6">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>16.58</v>
+        <v>31.96</v>
       </c>
       <c r="F7">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>96</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,13 +621,13 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>14.31</v>
+        <v>16.29</v>
       </c>
       <c r="E9">
-        <v>416.65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
+        <v>296.18</v>
+      </c>
+      <c r="F9">
+        <v>936</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-25/2026-10-25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-26/2026-10-26</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,418.00</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,215.37</t>
+  </si>
+  <si>
+    <t>2,203.90</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,261.55</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,549.18</t>
-  </si>
-  <si>
-    <t>2,544.79</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,255.61</t>
-  </si>
-  <si>
-    <t>3,252.11</t>
-  </si>
-  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,838.87</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,676.32</t>
-  </si>
-  <si>
-    <t>3,667.92</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,419.04</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,222.55</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>14,961.57</t>
-  </si>
-  <si>
-    <t>14,945.28</t>
+    <t>7,020.27</t>
+  </si>
+  <si>
+    <t>7,004.96</t>
   </si>
 </sst>
 </file>
@@ -498,136 +483,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31.16</v>
+        <v>88.69</v>
       </c>
       <c r="F3">
-        <v>151</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>3.5</v>
+        <v>11.47</v>
       </c>
       <c r="E4">
-        <v>159.6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>224</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>36.1</v>
+        <v>25.97</v>
       </c>
       <c r="F5">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>849.85</v>
+      </c>
+      <c r="C6">
+        <v>849.07</v>
       </c>
       <c r="D6">
-        <v>8.4</v>
+        <v>0.78</v>
       </c>
       <c r="E6">
-        <v>37.36</v>
+        <v>16.58</v>
       </c>
       <c r="F6">
-        <v>231</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>574.08</v>
+      </c>
+      <c r="C7">
+        <v>574.08</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>31.96</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>108</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>701.42</v>
+      </c>
+      <c r="C8">
+        <v>698.36</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>16.29</v>
+        <v>15.31</v>
       </c>
       <c r="E9">
-        <v>296.18</v>
+        <v>131.24</v>
       </c>
       <c r="F9">
-        <v>936</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-26/2026-10-26</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-27/2026-10-27</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,056.36</t>
+  </si>
+  <si>
+    <t>2,054.33</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,418.00</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,215.37</t>
-  </si>
-  <si>
-    <t>2,203.90</t>
+    <t>1,631.25</t>
+  </si>
+  <si>
+    <t>1,630.35</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,261.55</t>
+    <t>1,427.24</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,020.27</t>
-  </si>
-  <si>
-    <t>7,004.96</t>
+    <t>7,483.11</t>
+  </si>
+  <si>
+    <t>7,475.29</t>
   </si>
 </sst>
 </file>
@@ -483,136 +486,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="E3">
-        <v>88.69</v>
+        <v>28.76</v>
       </c>
       <c r="F3">
-        <v>102</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>11.47</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>61.92</v>
       </c>
       <c r="F4">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>25.97</v>
+        <v>70.22</v>
       </c>
       <c r="F5">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>849.85</v>
+        <v>744.88</v>
       </c>
       <c r="C6">
-        <v>849.07</v>
+        <v>739.99</v>
       </c>
       <c r="D6">
-        <v>0.78</v>
+        <v>4.89</v>
       </c>
       <c r="E6">
-        <v>16.58</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>574.08</v>
+        <v>683.28</v>
       </c>
       <c r="C7">
-        <v>574.08</v>
+        <v>683.28</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>34.18</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>701.42</v>
+        <v>940.1</v>
       </c>
       <c r="C8">
-        <v>698.36</v>
+        <v>940.1</v>
       </c>
       <c r="D8">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>10.49</v>
       </c>
       <c r="F8">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>15.31</v>
+        <v>7.82</v>
       </c>
       <c r="E9">
-        <v>131.24</v>
+        <v>205.57</v>
       </c>
       <c r="F9">
-        <v>514</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-27/2026-10-27</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-28/2026-10-28</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,46 +34,49 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,290.20</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,056.36</t>
-  </si>
-  <si>
-    <t>2,054.33</t>
+    <t>1,443.91</t>
+  </si>
+  <si>
+    <t>1,437.05</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,631.25</t>
-  </si>
-  <si>
-    <t>1,630.35</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,427.24</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,238.77</t>
+  </si>
+  <si>
+    <t>1,237.22</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>3,106.15</t>
+  </si>
+  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,483.11</t>
-  </si>
-  <si>
-    <t>7,475.29</t>
+    <t>8,447.43</t>
+  </si>
+  <si>
+    <t>8,434.75</t>
   </si>
 </sst>
 </file>
@@ -486,136 +489,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28.76</v>
+        <v>32.57</v>
       </c>
       <c r="F3">
-        <v>143</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>6.86</v>
       </c>
       <c r="E4">
-        <v>61.92</v>
+        <v>20.18</v>
       </c>
       <c r="F4">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>636.36</v>
+      </c>
+      <c r="C5">
+        <v>633.11</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="E5">
-        <v>70.22</v>
+        <v>17.7</v>
       </c>
       <c r="F5">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>744.88</v>
+        <v>732.04</v>
       </c>
       <c r="C6">
-        <v>739.99</v>
+        <v>731.02</v>
       </c>
       <c r="D6">
-        <v>4.89</v>
+        <v>1.02</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>683.28</v>
-      </c>
-      <c r="C7">
-        <v>683.28</v>
-      </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="E7">
-        <v>34.18</v>
+        <v>109.88</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
-        <v>940.1</v>
-      </c>
-      <c r="C8">
-        <v>940.1</v>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>10.49</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>7.82</v>
+        <v>12.68</v>
       </c>
       <c r="E9">
-        <v>205.57</v>
+        <v>180.33</v>
       </c>
       <c r="F9">
-        <v>528</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-28/2026-10-28</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-29/2026-10-29</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,49 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,266.88</t>
+  </si>
+  <si>
+    <t>1,264.84</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,663.30</t>
+  </si>
+  <si>
+    <t>1,659.18</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,505.96</t>
+  </si>
+  <si>
+    <t>1,505.06</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,290.20</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,443.91</t>
-  </si>
-  <si>
-    <t>1,437.05</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,238.77</t>
-  </si>
-  <si>
-    <t>1,237.22</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,106.15</t>
+    <t>1,023.99</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,447.43</t>
-  </si>
-  <si>
-    <t>8,434.75</t>
+    <t>7,012.10</t>
+  </si>
+  <si>
+    <t>7,001.82</t>
   </si>
 </sst>
 </file>
@@ -489,136 +492,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="E3">
-        <v>32.57</v>
+        <v>17.58</v>
       </c>
       <c r="F3">
-        <v>105</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>6.86</v>
+        <v>4.12</v>
       </c>
       <c r="E4">
-        <v>20.18</v>
+        <v>26.77</v>
       </c>
       <c r="F4">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>636.36</v>
-      </c>
-      <c r="C5">
-        <v>633.11</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>3.25</v>
+        <v>0.9</v>
       </c>
       <c r="E5">
-        <v>17.7</v>
+        <v>53.94</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>732.04</v>
+        <v>972.57</v>
       </c>
       <c r="C6">
-        <v>731.02</v>
+        <v>972.57</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>579.4</v>
+      </c>
+      <c r="C7">
+        <v>576.18</v>
       </c>
       <c r="D7">
-        <v>1.55</v>
+        <v>3.22</v>
       </c>
       <c r="E7">
-        <v>109.88</v>
+        <v>10.55</v>
       </c>
       <c r="F7">
-        <v>83</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32.96</v>
       </c>
       <c r="F8">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>12.68</v>
+        <v>10.28</v>
       </c>
       <c r="E9">
-        <v>180.33</v>
+        <v>141.8</v>
       </c>
       <c r="F9">
-        <v>446</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-10-29/2026-10-29</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-10-30/2026-10-30</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,49 +37,52 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,266.88</t>
-  </si>
-  <si>
-    <t>1,264.84</t>
+    <t>2,977.51</t>
+  </si>
+  <si>
+    <t>2,968.00</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,968.02</t>
+  </si>
+  <si>
+    <t>1,964.84</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,663.30</t>
-  </si>
-  <si>
-    <t>1,659.18</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,505.96</t>
-  </si>
-  <si>
-    <t>1,505.06</t>
+    <t>2,031.08</t>
+  </si>
+  <si>
+    <t>2,028.50</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,218.38</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,023.99</t>
+    <t>1,039.30</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,012.10</t>
-  </si>
-  <si>
-    <t>7,001.82</t>
+    <t>10,165.21</t>
+  </si>
+  <si>
+    <t>10,146.22</t>
   </si>
 </sst>
 </file>
@@ -495,133 +498,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.04</v>
+        <v>9.51</v>
       </c>
       <c r="E3">
-        <v>17.58</v>
+        <v>16.58</v>
       </c>
       <c r="F3">
-        <v>73</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>930.92</v>
+      </c>
+      <c r="C4">
+        <v>927.2</v>
       </c>
       <c r="D4">
-        <v>4.12</v>
+        <v>3.72</v>
       </c>
       <c r="E4">
-        <v>26.77</v>
+        <v>9.84</v>
       </c>
       <c r="F4">
-        <v>127</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>3.18</v>
       </c>
       <c r="E5">
-        <v>53.94</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>104</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
-        <v>972.57</v>
-      </c>
-      <c r="C6">
-        <v>972.57</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>58</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
-        <v>579.4</v>
-      </c>
-      <c r="C7">
-        <v>576.18</v>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10.55</v>
+        <v>23.97</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>32.96</v>
+        <v>23.37</v>
       </c>
       <c r="F8">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>10.28</v>
+        <v>18.99</v>
       </c>
       <c r="E9">
-        <v>141.8</v>
+        <v>73.76</v>
       </c>
       <c r="F9">
-        <v>493</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
